--- a/data/Escenarios_DCH_agosto/Costo_variable/Carga_on_board_variable_3estaciones_P640kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_agosto/Costo_variable/Carga_on_board_variable_3estaciones_P640kW/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_costos_nuevos\Costo_variable\Carga_on_board_fixed_3estaciones_P640kW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_agosto\Costo_variable\Carga_on_board_variable_3estaciones_P640kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C282AE48-D822-41D7-B7C8-292D83064281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAF2455-23B1-4D4D-B35B-A5B909C20A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12465" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="389">
   <si>
     <t>id</t>
   </si>
@@ -223,9 +223,6 @@
   </si>
   <si>
     <t>0.95</t>
-  </si>
-  <si>
-    <t>swap_time</t>
   </si>
   <si>
     <t>LH518B_2</t>
@@ -1577,7 +1574,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1780,6 +1777,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2086,7 +2084,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:BW17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="21" bestFit="1" customWidth="1"/>
@@ -2112,11 +2110,12 @@
     <col min="24" max="24" width="18.42578125" style="22" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="20.140625" style="22" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:75" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2186,29 +2185,26 @@
       <c r="W1" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="X1" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Y1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="Z1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="22" t="s">
+      <c r="AA1" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:75" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
@@ -2278,46 +2274,43 @@
       <c r="W2" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="X2" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="22" t="s">
+      <c r="Z2" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="AA2" s="22" t="s">
+      <c r="AA2" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="AD2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <v>1</v>
       </c>
       <c r="B3" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
-        <v>389</v>
+      <c r="C3" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3" s="7">
         <v>18</v>
@@ -2332,13 +2325,13 @@
         <v>20</v>
       </c>
       <c r="K3" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L3" s="7">
         <v>540</v>
       </c>
       <c r="M3" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N3" s="33">
         <v>-1</v>
@@ -2353,7 +2346,7 @@
         <v>-1</v>
       </c>
       <c r="R3" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S3" s="24">
         <v>0.92</v>
@@ -2365,48 +2358,48 @@
         <v>0.47</v>
       </c>
       <c r="V3" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W3" s="32">
         <v>4</v>
       </c>
-      <c r="X3" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y3" s="22">
+      <c r="X3" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y3" s="70">
         <v>4</v>
       </c>
-      <c r="Z3" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA3" s="22" t="s">
+      <c r="Z3" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA3" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AC3" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>389</v>
+        <v>62</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="7">
         <v>18</v>
@@ -2421,13 +2414,13 @@
         <v>20</v>
       </c>
       <c r="K4" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L4" s="7">
         <v>540</v>
       </c>
       <c r="M4" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N4" s="33">
         <v>-1</v>
@@ -2442,7 +2435,7 @@
         <v>-1</v>
       </c>
       <c r="R4" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S4" s="24">
         <v>0.92</v>
@@ -2454,48 +2447,48 @@
         <v>0.47</v>
       </c>
       <c r="V4" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W4" s="32">
         <v>4</v>
       </c>
-      <c r="X4" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y4" s="22">
+      <c r="X4" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y4" s="70">
         <v>4</v>
       </c>
-      <c r="Z4" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA4" s="22" t="s">
+      <c r="Z4" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA4" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>389</v>
+        <v>63</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" s="7">
         <v>18</v>
@@ -2510,13 +2503,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L5" s="7">
         <v>540</v>
       </c>
       <c r="M5" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N5" s="33">
         <v>-1</v>
@@ -2531,7 +2524,7 @@
         <v>-1</v>
       </c>
       <c r="R5" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S5" s="24">
         <v>0.92</v>
@@ -2543,48 +2536,48 @@
         <v>0.47</v>
       </c>
       <c r="V5" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W5" s="32">
         <v>4</v>
       </c>
-      <c r="X5" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y5" s="22">
+      <c r="X5" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y5" s="70">
         <v>4</v>
       </c>
-      <c r="Z5" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA5" s="22" t="s">
+      <c r="Z5" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA5" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AB5" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AC5" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29">
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>389</v>
+        <v>64</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" s="7">
         <v>18</v>
@@ -2599,13 +2592,13 @@
         <v>20</v>
       </c>
       <c r="K6" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L6" s="7">
         <v>540</v>
       </c>
       <c r="M6" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N6" s="33">
         <v>-1</v>
@@ -2620,7 +2613,7 @@
         <v>-1</v>
       </c>
       <c r="R6" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S6" s="24">
         <v>0.92</v>
@@ -2632,48 +2625,48 @@
         <v>0.47</v>
       </c>
       <c r="V6" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W6" s="32">
         <v>4</v>
       </c>
-      <c r="X6" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y6" s="22">
+      <c r="X6" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y6" s="70">
         <v>4</v>
       </c>
-      <c r="Z6" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA6" s="22" t="s">
+      <c r="Z6" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA6" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AB6" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AC6" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <v>5</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>352</v>
-      </c>
-      <c r="C7" t="s">
-        <v>389</v>
+        <v>351</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7" s="7">
         <v>18</v>
@@ -2688,13 +2681,13 @@
         <v>20</v>
       </c>
       <c r="K7" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L7" s="7">
         <v>540</v>
       </c>
       <c r="M7" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N7" s="33">
         <v>-1</v>
@@ -2709,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="R7" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S7" s="24">
         <v>0.92</v>
@@ -2721,48 +2714,48 @@
         <v>0.47</v>
       </c>
       <c r="V7" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W7" s="32">
         <v>4</v>
       </c>
-      <c r="X7" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y7" s="22">
+      <c r="X7" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y7" s="70">
         <v>4</v>
       </c>
-      <c r="Z7" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA7" s="22" t="s">
+      <c r="Z7" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA7" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AB7" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AC7" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <v>6</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>353</v>
-      </c>
-      <c r="C8" t="s">
-        <v>389</v>
+        <v>352</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8" s="7">
         <v>18</v>
@@ -2777,13 +2770,13 @@
         <v>20</v>
       </c>
       <c r="K8" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L8" s="7">
         <v>540</v>
       </c>
       <c r="M8" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N8" s="33">
         <v>-1</v>
@@ -2798,7 +2791,7 @@
         <v>-1</v>
       </c>
       <c r="R8" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S8" s="24">
         <v>0.92</v>
@@ -2810,48 +2803,48 @@
         <v>0.47</v>
       </c>
       <c r="V8" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W8" s="32">
         <v>4</v>
       </c>
-      <c r="X8" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y8" s="22">
+      <c r="X8" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y8" s="70">
         <v>4</v>
       </c>
-      <c r="Z8" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA8" s="22" t="s">
+      <c r="Z8" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA8" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AB8" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AC8" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>354</v>
-      </c>
-      <c r="C9" t="s">
-        <v>389</v>
+        <v>353</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9" s="7">
         <v>18</v>
@@ -2866,13 +2859,13 @@
         <v>20</v>
       </c>
       <c r="K9" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L9" s="7">
         <v>540</v>
       </c>
       <c r="M9" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N9" s="33">
         <v>-1</v>
@@ -2887,7 +2880,7 @@
         <v>-1</v>
       </c>
       <c r="R9" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S9" s="24">
         <v>0.92</v>
@@ -2899,48 +2892,48 @@
         <v>0.47</v>
       </c>
       <c r="V9" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W9" s="32">
         <v>4</v>
       </c>
-      <c r="X9" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y9" s="22">
+      <c r="X9" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y9" s="70">
         <v>4</v>
       </c>
-      <c r="Z9" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA9" s="22" t="s">
+      <c r="Z9" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA9" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AB9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AC9" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
         <v>8</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>355</v>
-      </c>
-      <c r="C10" t="s">
-        <v>389</v>
+        <v>354</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10" s="7">
         <v>18</v>
@@ -2955,13 +2948,13 @@
         <v>20</v>
       </c>
       <c r="K10" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L10" s="7">
         <v>540</v>
       </c>
       <c r="M10" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N10" s="33">
         <v>-1</v>
@@ -2976,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="R10" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S10" s="24">
         <v>0.92</v>
@@ -2988,48 +2981,48 @@
         <v>0.47</v>
       </c>
       <c r="V10" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W10" s="32">
         <v>4</v>
       </c>
-      <c r="X10" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y10" s="22">
+      <c r="X10" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y10" s="70">
         <v>4</v>
       </c>
-      <c r="Z10" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA10" s="22" t="s">
+      <c r="Z10" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA10" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AB10" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AC10" s="32" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:75" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <v>9</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>356</v>
-      </c>
-      <c r="C11" t="s">
-        <v>389</v>
+        <v>355</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="7">
         <v>18</v>
@@ -3044,13 +3037,13 @@
         <v>20</v>
       </c>
       <c r="K11" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L11" s="7">
         <v>540</v>
       </c>
       <c r="M11" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N11" s="33">
         <v>-1</v>
@@ -3065,7 +3058,7 @@
         <v>-1</v>
       </c>
       <c r="R11" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S11" s="24">
         <v>0.92</v>
@@ -3077,49 +3070,94 @@
         <v>0.47</v>
       </c>
       <c r="V11" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W11" s="32">
         <v>4</v>
       </c>
-      <c r="X11" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y11" s="22">
+      <c r="X11" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y11" s="70">
         <v>4</v>
       </c>
-      <c r="Z11" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA11" s="22" t="s">
+      <c r="Z11" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA11" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AB11" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AC11" s="32" t="s">
         <v>61</v>
       </c>
       <c r="AD11"/>
-    </row>
-    <row r="12" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+      <c r="AI11"/>
+      <c r="AJ11"/>
+      <c r="AK11"/>
+      <c r="AL11"/>
+      <c r="AM11"/>
+      <c r="AN11"/>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11"/>
+      <c r="AS11"/>
+      <c r="AT11"/>
+      <c r="AU11"/>
+      <c r="AV11"/>
+      <c r="AW11"/>
+      <c r="AX11"/>
+      <c r="AY11"/>
+      <c r="AZ11"/>
+      <c r="BA11"/>
+      <c r="BB11"/>
+      <c r="BC11"/>
+      <c r="BD11"/>
+      <c r="BE11"/>
+      <c r="BF11"/>
+      <c r="BG11"/>
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
+      <c r="BK11"/>
+      <c r="BL11"/>
+      <c r="BM11"/>
+      <c r="BN11"/>
+      <c r="BO11"/>
+      <c r="BP11"/>
+      <c r="BQ11"/>
+      <c r="BR11"/>
+      <c r="BS11"/>
+      <c r="BT11"/>
+      <c r="BU11"/>
+      <c r="BV11"/>
+      <c r="BW11"/>
+    </row>
+    <row r="12" spans="1:75" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="29">
         <v>10</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>357</v>
-      </c>
-      <c r="C12" t="s">
-        <v>389</v>
+        <v>356</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" s="7">
         <v>18</v>
@@ -3134,13 +3172,13 @@
         <v>20</v>
       </c>
       <c r="K12" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L12" s="7">
         <v>540</v>
       </c>
       <c r="M12" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N12" s="33">
         <v>-1</v>
@@ -3155,7 +3193,7 @@
         <v>-1</v>
       </c>
       <c r="R12" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S12" s="24">
         <v>0.92</v>
@@ -3167,49 +3205,94 @@
         <v>0.47</v>
       </c>
       <c r="V12" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W12" s="32">
         <v>4</v>
       </c>
-      <c r="X12" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y12" s="22">
+      <c r="X12" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y12" s="70">
         <v>4</v>
       </c>
-      <c r="Z12" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA12" s="22" t="s">
+      <c r="Z12" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA12" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AB12" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AC12" s="32" t="s">
         <v>61</v>
       </c>
       <c r="AD12"/>
-    </row>
-    <row r="13" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE12"/>
+      <c r="AF12"/>
+      <c r="AG12"/>
+      <c r="AH12"/>
+      <c r="AI12"/>
+      <c r="AJ12"/>
+      <c r="AK12"/>
+      <c r="AL12"/>
+      <c r="AM12"/>
+      <c r="AN12"/>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+      <c r="AR12"/>
+      <c r="AS12"/>
+      <c r="AT12"/>
+      <c r="AU12"/>
+      <c r="AV12"/>
+      <c r="AW12"/>
+      <c r="AX12"/>
+      <c r="AY12"/>
+      <c r="AZ12"/>
+      <c r="BA12"/>
+      <c r="BB12"/>
+      <c r="BC12"/>
+      <c r="BD12"/>
+      <c r="BE12"/>
+      <c r="BF12"/>
+      <c r="BG12"/>
+      <c r="BH12"/>
+      <c r="BI12"/>
+      <c r="BJ12"/>
+      <c r="BK12"/>
+      <c r="BL12"/>
+      <c r="BM12"/>
+      <c r="BN12"/>
+      <c r="BO12"/>
+      <c r="BP12"/>
+      <c r="BQ12"/>
+      <c r="BR12"/>
+      <c r="BS12"/>
+      <c r="BT12"/>
+      <c r="BU12"/>
+      <c r="BV12"/>
+      <c r="BW12"/>
+    </row>
+    <row r="13" spans="1:75" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29">
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>358</v>
-      </c>
-      <c r="C13" t="s">
-        <v>389</v>
+        <v>357</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="7">
         <v>18</v>
@@ -3224,13 +3307,13 @@
         <v>20</v>
       </c>
       <c r="K13" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L13" s="7">
         <v>540</v>
       </c>
       <c r="M13" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N13" s="33">
         <v>-1</v>
@@ -3245,7 +3328,7 @@
         <v>-1</v>
       </c>
       <c r="R13" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S13" s="24">
         <v>0.92</v>
@@ -3257,49 +3340,94 @@
         <v>0.47</v>
       </c>
       <c r="V13" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W13" s="32">
         <v>4</v>
       </c>
-      <c r="X13" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y13" s="22">
+      <c r="X13" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y13" s="70">
         <v>4</v>
       </c>
-      <c r="Z13" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA13" s="22" t="s">
+      <c r="Z13" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA13" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AB13" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AC13" s="32" t="s">
         <v>61</v>
       </c>
       <c r="AD13"/>
-    </row>
-    <row r="14" spans="1:30" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
+      <c r="AH13"/>
+      <c r="AI13"/>
+      <c r="AJ13"/>
+      <c r="AK13"/>
+      <c r="AL13"/>
+      <c r="AM13"/>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13"/>
+      <c r="AS13"/>
+      <c r="AT13"/>
+      <c r="AU13"/>
+      <c r="AV13"/>
+      <c r="AW13"/>
+      <c r="AX13"/>
+      <c r="AY13"/>
+      <c r="AZ13"/>
+      <c r="BA13"/>
+      <c r="BB13"/>
+      <c r="BC13"/>
+      <c r="BD13"/>
+      <c r="BE13"/>
+      <c r="BF13"/>
+      <c r="BG13"/>
+      <c r="BH13"/>
+      <c r="BI13"/>
+      <c r="BJ13"/>
+      <c r="BK13"/>
+      <c r="BL13"/>
+      <c r="BM13"/>
+      <c r="BN13"/>
+      <c r="BO13"/>
+      <c r="BP13"/>
+      <c r="BQ13"/>
+      <c r="BR13"/>
+      <c r="BS13"/>
+      <c r="BT13"/>
+      <c r="BU13"/>
+      <c r="BV13"/>
+      <c r="BW13"/>
+    </row>
+    <row r="14" spans="1:75" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29">
         <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>359</v>
-      </c>
-      <c r="C14" t="s">
-        <v>389</v>
+        <v>358</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>388</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>52</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="7">
         <v>18</v>
@@ -3314,13 +3442,13 @@
         <v>20</v>
       </c>
       <c r="K14" s="7">
-        <v>52</v>
+        <v>54.8</v>
       </c>
       <c r="L14" s="7">
         <v>540</v>
       </c>
       <c r="M14" s="20">
-        <v>6.26</v>
+        <v>8.73</v>
       </c>
       <c r="N14" s="33">
         <v>-1</v>
@@ -3335,7 +3463,7 @@
         <v>-1</v>
       </c>
       <c r="R14" s="20">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="S14" s="24">
         <v>0.92</v>
@@ -3347,33 +3475,78 @@
         <v>0.47</v>
       </c>
       <c r="V14" s="32">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="W14" s="32">
         <v>4</v>
       </c>
-      <c r="X14" s="22">
-        <v>360</v>
-      </c>
-      <c r="Y14" s="22">
+      <c r="X14" s="70">
+        <v>320</v>
+      </c>
+      <c r="Y14" s="70">
         <v>4</v>
       </c>
-      <c r="Z14" s="22">
-        <v>353</v>
-      </c>
-      <c r="AA14" s="22" t="s">
+      <c r="Z14" s="70">
+        <v>482</v>
+      </c>
+      <c r="AA14" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AB14" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AC14" s="32" t="s">
         <v>61</v>
       </c>
       <c r="AD14"/>
-    </row>
-    <row r="15" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+      <c r="AG14"/>
+      <c r="AH14"/>
+      <c r="AI14"/>
+      <c r="AJ14"/>
+      <c r="AK14"/>
+      <c r="AL14"/>
+      <c r="AM14"/>
+      <c r="AN14"/>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14"/>
+      <c r="AS14"/>
+      <c r="AT14"/>
+      <c r="AU14"/>
+      <c r="AV14"/>
+      <c r="AW14"/>
+      <c r="AX14"/>
+      <c r="AY14"/>
+      <c r="AZ14"/>
+      <c r="BA14"/>
+      <c r="BB14"/>
+      <c r="BC14"/>
+      <c r="BD14"/>
+      <c r="BE14"/>
+      <c r="BF14"/>
+      <c r="BG14"/>
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
+      <c r="BK14"/>
+      <c r="BL14"/>
+      <c r="BM14"/>
+      <c r="BN14"/>
+      <c r="BO14"/>
+      <c r="BP14"/>
+      <c r="BQ14"/>
+      <c r="BR14"/>
+      <c r="BS14"/>
+      <c r="BT14"/>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
+    </row>
+    <row r="15" spans="1:75" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:75" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -3395,132 +3568,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>372</v>
       </c>
-      <c r="C1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D1" t="s">
-        <v>385</v>
-      </c>
-      <c r="E1" t="s">
-        <v>386</v>
-      </c>
-      <c r="F1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G1" t="s">
-        <v>388</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="D2" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="32">
+        <v>1</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="C3" s="32">
+        <v>32711</v>
+      </c>
+      <c r="D3" s="32">
+        <v>35000</v>
+      </c>
+      <c r="E3" s="32">
+        <v>5250</v>
+      </c>
+      <c r="F3" s="32">
+        <v>2</v>
+      </c>
+      <c r="G3" s="32">
+        <v>1</v>
+      </c>
+      <c r="H3" s="32">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="32">
+        <v>2</v>
+      </c>
+      <c r="B4" s="32" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C4" s="32">
+        <v>32711</v>
+      </c>
+      <c r="D4" s="32">
+        <v>35000</v>
+      </c>
+      <c r="E4" s="32">
+        <v>5250</v>
+      </c>
+      <c r="F4" s="32">
+        <v>2</v>
+      </c>
+      <c r="G4" s="32">
+        <v>1</v>
+      </c>
+      <c r="H4" s="32">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="32">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B5" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="32">
+        <v>32711</v>
+      </c>
+      <c r="D5" s="32">
+        <v>35000</v>
+      </c>
+      <c r="E5" s="32">
+        <v>5250</v>
+      </c>
+      <c r="F5" s="32">
+        <v>2</v>
+      </c>
+      <c r="G5" s="32">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C3">
-        <v>35722</v>
-      </c>
-      <c r="D3">
-        <v>38221</v>
-      </c>
-      <c r="E3">
-        <v>5733</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>382</v>
-      </c>
-      <c r="C4">
-        <v>35722</v>
-      </c>
-      <c r="D4">
-        <v>38221</v>
-      </c>
-      <c r="E4">
-        <v>5733</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C5">
-        <v>35722</v>
-      </c>
-      <c r="D5">
-        <v>38221</v>
-      </c>
-      <c r="E5">
-        <v>5733</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
+      <c r="H5" s="32">
         <v>1500</v>
       </c>
     </row>
@@ -3534,64 +3707,70 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="25" t="s">
         <v>376</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="25" t="s">
         <v>378</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="32">
+        <v>1</v>
+      </c>
+      <c r="B3" s="32" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="C3" s="32">
+        <v>74771</v>
+      </c>
+      <c r="D3" s="32">
+        <v>640</v>
+      </c>
+      <c r="E3" s="32">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C3">
-        <v>84143</v>
-      </c>
-      <c r="D3">
-        <v>640</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="F3" s="32">
         <v>5000</v>
       </c>
     </row>
@@ -3673,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>6</v>
@@ -3699,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C4" s="65" t="s">
         <v>6</v>
@@ -3725,7 +3904,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="65" t="s">
         <v>6</v>
@@ -3751,7 +3930,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C6" s="65" t="s">
         <v>6</v>
@@ -3777,7 +3956,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C7" s="65" t="s">
         <v>6</v>
@@ -3803,7 +3982,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="65" t="s">
         <v>6</v>
@@ -3829,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9" s="65" t="s">
         <v>6</v>
@@ -3855,7 +4034,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C10" s="65" t="s">
         <v>6</v>
@@ -3881,7 +4060,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="65" t="s">
         <v>6</v>
@@ -3907,7 +4086,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C12" s="65" t="s">
         <v>6</v>
@@ -3933,7 +4112,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C13" s="65" t="s">
         <v>6</v>
@@ -3959,7 +4138,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C14" s="65" t="s">
         <v>6</v>
@@ -3985,7 +4164,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="65" t="s">
         <v>6</v>
@@ -4011,7 +4190,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C16" s="65" t="s">
         <v>6</v>
@@ -4037,7 +4216,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C17" s="65" t="s">
         <v>6</v>
@@ -4063,7 +4242,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C18" s="65" t="s">
         <v>6</v>
@@ -4089,7 +4268,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C19" s="65" t="s">
         <v>6</v>
@@ -4115,7 +4294,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C20" s="65" t="s">
         <v>6</v>
@@ -4141,7 +4320,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C21" s="65" t="s">
         <v>6</v>
@@ -4167,7 +4346,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C22" s="65" t="s">
         <v>6</v>
@@ -4193,7 +4372,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C23" s="65" t="s">
         <v>6</v>
@@ -4219,7 +4398,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C24" s="65" t="s">
         <v>6</v>
@@ -4245,7 +4424,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C25" s="65" t="s">
         <v>6</v>
@@ -4271,7 +4450,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="65" t="s">
         <v>13</v>
@@ -4297,7 +4476,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C27" s="65" t="s">
         <v>13</v>
@@ -4323,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C28" s="65" t="s">
         <v>13</v>
@@ -4349,7 +4528,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C29" s="65" t="s">
         <v>13</v>
@@ -4375,7 +4554,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C30" s="65" t="s">
         <v>13</v>
@@ -4401,7 +4580,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C31" s="65" t="s">
         <v>13</v>
@@ -4427,7 +4606,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C32" s="65" t="s">
         <v>13</v>
@@ -4453,7 +4632,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="65" t="s">
         <v>13</v>
@@ -4479,7 +4658,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34" s="65" t="s">
         <v>13</v>
@@ -4505,7 +4684,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C35" s="65" t="s">
         <v>13</v>
@@ -4531,7 +4710,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C36" s="65" t="s">
         <v>13</v>
@@ -4557,7 +4736,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C37" s="65" t="s">
         <v>13</v>
@@ -4583,7 +4762,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" s="65" t="s">
         <v>13</v>
@@ -4609,7 +4788,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C39" s="65" t="s">
         <v>13</v>
@@ -4635,7 +4814,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="44" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C40" s="65" t="s">
         <v>13</v>
@@ -4661,7 +4840,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C41" s="65" t="s">
         <v>13</v>
@@ -4687,7 +4866,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C42" s="65" t="s">
         <v>13</v>
@@ -4713,7 +4892,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="44" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C43" s="65" t="s">
         <v>13</v>
@@ -4739,7 +4918,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C44" s="65" t="s">
         <v>13</v>
@@ -4765,7 +4944,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C45" s="65" t="s">
         <v>13</v>
@@ -4791,7 +4970,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C46" s="65" t="s">
         <v>13</v>
@@ -4817,7 +4996,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C47" s="65" t="s">
         <v>13</v>
@@ -4843,7 +5022,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C48" s="65" t="s">
         <v>13</v>
@@ -4869,7 +5048,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C49" s="65" t="s">
         <v>13</v>
@@ -4895,7 +5074,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C50" s="65" t="s">
         <v>14</v>
@@ -4921,7 +5100,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C51" s="65" t="s">
         <v>14</v>
@@ -4947,7 +5126,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C52" s="65" t="s">
         <v>14</v>
@@ -4973,7 +5152,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C53" s="65" t="s">
         <v>14</v>
@@ -4999,7 +5178,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C54" s="65" t="s">
         <v>14</v>
@@ -5025,7 +5204,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C55" s="65" t="s">
         <v>14</v>
@@ -5051,7 +5230,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C56" s="65" t="s">
         <v>14</v>
@@ -5077,7 +5256,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C57" s="65" t="s">
         <v>14</v>
@@ -5103,7 +5282,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C58" s="65" t="s">
         <v>14</v>
@@ -5129,7 +5308,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C59" s="65" t="s">
         <v>14</v>
@@ -5155,7 +5334,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C60" s="65" t="s">
         <v>14</v>
@@ -5181,7 +5360,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C61" s="65" t="s">
         <v>14</v>
@@ -5207,7 +5386,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C62" s="65" t="s">
         <v>14</v>
@@ -5233,7 +5412,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C63" s="65" t="s">
         <v>14</v>
@@ -5259,7 +5438,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C64" s="65" t="s">
         <v>14</v>
@@ -5285,7 +5464,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C65" s="65" t="s">
         <v>14</v>
@@ -5311,7 +5490,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C66" s="65" t="s">
         <v>14</v>
@@ -5337,7 +5516,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C67" s="65" t="s">
         <v>14</v>
@@ -5363,7 +5542,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C68" s="65" t="s">
         <v>14</v>
@@ -5389,7 +5568,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C69" s="65" t="s">
         <v>14</v>
@@ -5415,7 +5594,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C70" s="65" t="s">
         <v>14</v>
@@ -5441,7 +5620,7 @@
         <v>68</v>
       </c>
       <c r="B71" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C71" s="65" t="s">
         <v>14</v>
@@ -5467,7 +5646,7 @@
         <v>69</v>
       </c>
       <c r="B72" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C72" s="65" t="s">
         <v>14</v>
@@ -5493,7 +5672,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C73" s="65" t="s">
         <v>14</v>
@@ -5519,7 +5698,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C74" s="65" t="s">
         <v>15</v>
@@ -5545,7 +5724,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C75" s="65" t="s">
         <v>15</v>
@@ -5571,7 +5750,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C76" s="65" t="s">
         <v>15</v>
@@ -5597,7 +5776,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C77" s="65" t="s">
         <v>15</v>
@@ -5623,7 +5802,7 @@
         <v>75</v>
       </c>
       <c r="B78" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C78" s="65" t="s">
         <v>15</v>
@@ -5649,7 +5828,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C79" s="65" t="s">
         <v>15</v>
@@ -5675,7 +5854,7 @@
         <v>77</v>
       </c>
       <c r="B80" s="44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C80" s="65" t="s">
         <v>15</v>
@@ -5701,7 +5880,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C81" s="65" t="s">
         <v>15</v>
@@ -5727,7 +5906,7 @@
         <v>79</v>
       </c>
       <c r="B82" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C82" s="65" t="s">
         <v>15</v>
@@ -5753,7 +5932,7 @@
         <v>80</v>
       </c>
       <c r="B83" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C83" s="65" t="s">
         <v>15</v>
@@ -5779,7 +5958,7 @@
         <v>81</v>
       </c>
       <c r="B84" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C84" s="65" t="s">
         <v>15</v>
@@ -5805,7 +5984,7 @@
         <v>82</v>
       </c>
       <c r="B85" s="44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C85" s="65" t="s">
         <v>15</v>
@@ -5831,7 +6010,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C86" s="65" t="s">
         <v>15</v>
@@ -5857,7 +6036,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C87" s="65" t="s">
         <v>15</v>
@@ -5883,7 +6062,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C88" s="65" t="s">
         <v>15</v>
@@ -5909,7 +6088,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C89" s="65" t="s">
         <v>15</v>
@@ -5935,7 +6114,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C90" s="65" t="s">
         <v>15</v>
@@ -5961,7 +6140,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C91" s="65" t="s">
         <v>15</v>
@@ -5987,7 +6166,7 @@
         <v>89</v>
       </c>
       <c r="B92" s="44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C92" s="65" t="s">
         <v>15</v>
@@ -6013,7 +6192,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="44" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C93" s="65" t="s">
         <v>15</v>
@@ -6039,7 +6218,7 @@
         <v>91</v>
       </c>
       <c r="B94" s="44" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C94" s="65" t="s">
         <v>15</v>
@@ -6065,7 +6244,7 @@
         <v>92</v>
       </c>
       <c r="B95" s="44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C95" s="65" t="s">
         <v>15</v>
@@ -6091,7 +6270,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C96" s="65" t="s">
         <v>15</v>
@@ -6117,10 +6296,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C97" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D97" s="47" t="s">
         <v>5</v>
@@ -6143,10 +6322,10 @@
         <v>95</v>
       </c>
       <c r="B98" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C98" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D98" s="47" t="s">
         <v>5</v>
@@ -6169,10 +6348,10 @@
         <v>96</v>
       </c>
       <c r="B99" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C99" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D99" s="47" t="s">
         <v>5</v>
@@ -6195,10 +6374,10 @@
         <v>97</v>
       </c>
       <c r="B100" s="42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C100" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D100" s="47" t="s">
         <v>5</v>
@@ -6221,10 +6400,10 @@
         <v>98</v>
       </c>
       <c r="B101" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C101" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D101" s="47" t="s">
         <v>5</v>
@@ -6247,10 +6426,10 @@
         <v>99</v>
       </c>
       <c r="B102" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C102" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D102" s="47" t="s">
         <v>5</v>
@@ -6273,10 +6452,10 @@
         <v>100</v>
       </c>
       <c r="B103" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C103" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D103" s="47" t="s">
         <v>5</v>
@@ -6299,10 +6478,10 @@
         <v>101</v>
       </c>
       <c r="B104" s="42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C104" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D104" s="47" t="s">
         <v>5</v>
@@ -6325,10 +6504,10 @@
         <v>102</v>
       </c>
       <c r="B105" s="42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C105" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D105" s="47" t="s">
         <v>5</v>
@@ -6351,10 +6530,10 @@
         <v>103</v>
       </c>
       <c r="B106" s="42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C106" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D106" s="47" t="s">
         <v>5</v>
@@ -6377,10 +6556,10 @@
         <v>104</v>
       </c>
       <c r="B107" s="42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C107" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D107" s="47" t="s">
         <v>5</v>
@@ -6403,10 +6582,10 @@
         <v>105</v>
       </c>
       <c r="B108" s="42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C108" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D108" s="47" t="s">
         <v>5</v>
@@ -6429,10 +6608,10 @@
         <v>106</v>
       </c>
       <c r="B109" s="42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C109" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D109" s="47" t="s">
         <v>5</v>
@@ -6455,10 +6634,10 @@
         <v>107</v>
       </c>
       <c r="B110" s="42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C110" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D110" s="47" t="s">
         <v>5</v>
@@ -6481,10 +6660,10 @@
         <v>108</v>
       </c>
       <c r="B111" s="42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C111" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D111" s="47" t="s">
         <v>5</v>
@@ -6507,10 +6686,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C112" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D112" s="47" t="s">
         <v>5</v>
@@ -6533,10 +6712,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C113" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D113" s="47" t="s">
         <v>5</v>
@@ -6559,10 +6738,10 @@
         <v>111</v>
       </c>
       <c r="B114" s="42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C114" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D114" s="47" t="s">
         <v>5</v>
@@ -6585,10 +6764,10 @@
         <v>112</v>
       </c>
       <c r="B115" s="42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C115" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D115" s="47" t="s">
         <v>5</v>
@@ -6611,10 +6790,10 @@
         <v>113</v>
       </c>
       <c r="B116" s="42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C116" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D116" s="47" t="s">
         <v>5</v>
@@ -6637,10 +6816,10 @@
         <v>114</v>
       </c>
       <c r="B117" s="42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C117" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D117" s="47" t="s">
         <v>5</v>
@@ -6663,10 +6842,10 @@
         <v>115</v>
       </c>
       <c r="B118" s="42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C118" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D118" s="47" t="s">
         <v>5</v>
@@ -6689,10 +6868,10 @@
         <v>116</v>
       </c>
       <c r="B119" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C119" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D119" s="47" t="s">
         <v>5</v>
@@ -6715,10 +6894,10 @@
         <v>117</v>
       </c>
       <c r="B120" s="42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C120" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D120" s="47" t="s">
         <v>5</v>
@@ -6741,10 +6920,10 @@
         <v>118</v>
       </c>
       <c r="B121" s="42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C121" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D121" s="47" t="s">
         <v>5</v>
@@ -6767,10 +6946,10 @@
         <v>119</v>
       </c>
       <c r="B122" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C122" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D122" s="47" t="s">
         <v>5</v>
@@ -6793,10 +6972,10 @@
         <v>120</v>
       </c>
       <c r="B123" s="42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C123" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D123" s="47" t="s">
         <v>5</v>
@@ -6819,10 +6998,10 @@
         <v>121</v>
       </c>
       <c r="B124" s="42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C124" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D124" s="47" t="s">
         <v>5</v>
@@ -6845,10 +7024,10 @@
         <v>122</v>
       </c>
       <c r="B125" s="42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C125" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D125" s="47" t="s">
         <v>5</v>
@@ -6871,10 +7050,10 @@
         <v>123</v>
       </c>
       <c r="B126" s="42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C126" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D126" s="47" t="s">
         <v>5</v>
@@ -6897,10 +7076,10 @@
         <v>124</v>
       </c>
       <c r="B127" s="42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C127" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D127" s="47" t="s">
         <v>5</v>
@@ -6923,10 +7102,10 @@
         <v>125</v>
       </c>
       <c r="B128" s="42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C128" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D128" s="47" t="s">
         <v>5</v>
@@ -6949,10 +7128,10 @@
         <v>126</v>
       </c>
       <c r="B129" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C129" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D129" s="47" t="s">
         <v>5</v>
@@ -6975,10 +7154,10 @@
         <v>127</v>
       </c>
       <c r="B130" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C130" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D130" s="47" t="s">
         <v>5</v>
@@ -7001,10 +7180,10 @@
         <v>128</v>
       </c>
       <c r="B131" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C131" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D131" s="47" t="s">
         <v>5</v>
@@ -7027,10 +7206,10 @@
         <v>129</v>
       </c>
       <c r="B132" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C132" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D132" s="47" t="s">
         <v>5</v>
@@ -7053,10 +7232,10 @@
         <v>130</v>
       </c>
       <c r="B133" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C133" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D133" s="47" t="s">
         <v>5</v>
@@ -7079,10 +7258,10 @@
         <v>131</v>
       </c>
       <c r="B134" s="42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C134" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D134" s="47" t="s">
         <v>5</v>
@@ -7105,10 +7284,10 @@
         <v>132</v>
       </c>
       <c r="B135" s="42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C135" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D135" s="47" t="s">
         <v>5</v>
@@ -7131,10 +7310,10 @@
         <v>133</v>
       </c>
       <c r="B136" s="42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C136" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D136" s="47" t="s">
         <v>5</v>
@@ -7157,10 +7336,10 @@
         <v>134</v>
       </c>
       <c r="B137" s="43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C137" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D137" s="47" t="s">
         <v>5</v>
@@ -7183,10 +7362,10 @@
         <v>135</v>
       </c>
       <c r="B138" s="43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C138" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D138" s="47" t="s">
         <v>5</v>
@@ -7209,10 +7388,10 @@
         <v>136</v>
       </c>
       <c r="B139" s="43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C139" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D139" s="47" t="s">
         <v>5</v>
@@ -7235,10 +7414,10 @@
         <v>137</v>
       </c>
       <c r="B140" s="43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C140" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D140" s="47" t="s">
         <v>5</v>
@@ -7261,10 +7440,10 @@
         <v>138</v>
       </c>
       <c r="B141" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C141" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D141" s="47" t="s">
         <v>5</v>
@@ -7287,10 +7466,10 @@
         <v>139</v>
       </c>
       <c r="B142" s="43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C142" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D142" s="47" t="s">
         <v>5</v>
@@ -7313,10 +7492,10 @@
         <v>140</v>
       </c>
       <c r="B143" s="43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C143" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D143" s="47" t="s">
         <v>5</v>
@@ -7339,10 +7518,10 @@
         <v>141</v>
       </c>
       <c r="B144" s="43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C144" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D144" s="47" t="s">
         <v>5</v>
@@ -7365,10 +7544,10 @@
         <v>142</v>
       </c>
       <c r="B145" s="43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C145" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D145" s="47" t="s">
         <v>5</v>
@@ -7391,10 +7570,10 @@
         <v>143</v>
       </c>
       <c r="B146" s="43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C146" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D146" s="47" t="s">
         <v>5</v>
@@ -7417,10 +7596,10 @@
         <v>144</v>
       </c>
       <c r="B147" s="43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C147" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D147" s="47" t="s">
         <v>5</v>
@@ -7443,10 +7622,10 @@
         <v>145</v>
       </c>
       <c r="B148" s="43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C148" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D148" s="47" t="s">
         <v>5</v>
@@ -7469,10 +7648,10 @@
         <v>146</v>
       </c>
       <c r="B149" s="43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C149" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D149" s="47" t="s">
         <v>5</v>
@@ -7495,10 +7674,10 @@
         <v>147</v>
       </c>
       <c r="B150" s="43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C150" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D150" s="47" t="s">
         <v>5</v>
@@ -7521,10 +7700,10 @@
         <v>148</v>
       </c>
       <c r="B151" s="43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C151" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D151" s="47" t="s">
         <v>5</v>
@@ -7547,10 +7726,10 @@
         <v>149</v>
       </c>
       <c r="B152" s="43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C152" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D152" s="47" t="s">
         <v>5</v>
@@ -7573,10 +7752,10 @@
         <v>150</v>
       </c>
       <c r="B153" s="43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C153" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D153" s="47" t="s">
         <v>5</v>
@@ -7599,10 +7778,10 @@
         <v>151</v>
       </c>
       <c r="B154" s="43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C154" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D154" s="47" t="s">
         <v>5</v>
@@ -7625,10 +7804,10 @@
         <v>152</v>
       </c>
       <c r="B155" s="43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C155" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D155" s="47" t="s">
         <v>5</v>
@@ -7651,10 +7830,10 @@
         <v>153</v>
       </c>
       <c r="B156" s="43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C156" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D156" s="47" t="s">
         <v>5</v>
@@ -7677,10 +7856,10 @@
         <v>154</v>
       </c>
       <c r="B157" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C157" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D157" s="47" t="s">
         <v>5</v>
@@ -7703,10 +7882,10 @@
         <v>155</v>
       </c>
       <c r="B158" s="43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C158" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D158" s="47" t="s">
         <v>5</v>
@@ -7729,10 +7908,10 @@
         <v>156</v>
       </c>
       <c r="B159" s="43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C159" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D159" s="47" t="s">
         <v>5</v>
@@ -7755,10 +7934,10 @@
         <v>157</v>
       </c>
       <c r="B160" s="43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C160" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D160" s="47" t="s">
         <v>5</v>
@@ -7781,10 +7960,10 @@
         <v>158</v>
       </c>
       <c r="B161" s="43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C161" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D161" s="47" t="s">
         <v>5</v>
@@ -7807,10 +7986,10 @@
         <v>159</v>
       </c>
       <c r="B162" s="43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C162" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D162" s="47" t="s">
         <v>5</v>
@@ -7833,10 +8012,10 @@
         <v>160</v>
       </c>
       <c r="B163" s="43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C163" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D163" s="47" t="s">
         <v>5</v>
@@ -7859,10 +8038,10 @@
         <v>161</v>
       </c>
       <c r="B164" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C164" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D164" s="47" t="s">
         <v>5</v>
@@ -7885,10 +8064,10 @@
         <v>162</v>
       </c>
       <c r="B165" s="43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C165" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D165" s="47" t="s">
         <v>5</v>
@@ -7911,10 +8090,10 @@
         <v>163</v>
       </c>
       <c r="B166" s="43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C166" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D166" s="47" t="s">
         <v>5</v>
@@ -7937,10 +8116,10 @@
         <v>164</v>
       </c>
       <c r="B167" s="43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C167" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D167" s="47" t="s">
         <v>5</v>
@@ -7963,10 +8142,10 @@
         <v>165</v>
       </c>
       <c r="B168" s="43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C168" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D168" s="47" t="s">
         <v>5</v>
@@ -7989,10 +8168,10 @@
         <v>166</v>
       </c>
       <c r="B169" s="43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C169" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D169" s="47" t="s">
         <v>5</v>
@@ -8015,10 +8194,10 @@
         <v>167</v>
       </c>
       <c r="B170" s="43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C170" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D170" s="47" t="s">
         <v>5</v>
@@ -8041,10 +8220,10 @@
         <v>168</v>
       </c>
       <c r="B171" s="43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C171" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D171" s="47" t="s">
         <v>5</v>
@@ -8067,10 +8246,10 @@
         <v>169</v>
       </c>
       <c r="B172" s="43" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C172" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D172" s="47" t="s">
         <v>5</v>
@@ -8093,10 +8272,10 @@
         <v>170</v>
       </c>
       <c r="B173" s="43" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C173" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D173" s="47" t="s">
         <v>5</v>
@@ -8119,10 +8298,10 @@
         <v>171</v>
       </c>
       <c r="B174" s="43" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C174" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D174" s="47" t="s">
         <v>5</v>
@@ -8145,10 +8324,10 @@
         <v>172</v>
       </c>
       <c r="B175" s="43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C175" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D175" s="47" t="s">
         <v>5</v>
@@ -8171,10 +8350,10 @@
         <v>173</v>
       </c>
       <c r="B176" s="43" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C176" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D176" s="47" t="s">
         <v>5</v>
@@ -8197,10 +8376,10 @@
         <v>174</v>
       </c>
       <c r="B177" s="43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C177" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D177" s="47" t="s">
         <v>5</v>
@@ -8223,10 +8402,10 @@
         <v>175</v>
       </c>
       <c r="B178" s="43" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C178" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D178" s="47" t="s">
         <v>5</v>
@@ -8249,10 +8428,10 @@
         <v>176</v>
       </c>
       <c r="B179" s="43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C179" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D179" s="47" t="s">
         <v>5</v>
@@ -8275,10 +8454,10 @@
         <v>177</v>
       </c>
       <c r="B180" s="43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C180" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D180" s="47" t="s">
         <v>5</v>
@@ -8301,10 +8480,10 @@
         <v>178</v>
       </c>
       <c r="B181" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C181" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D181" s="47" t="s">
         <v>5</v>
@@ -8327,10 +8506,10 @@
         <v>179</v>
       </c>
       <c r="B182" s="43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C182" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D182" s="47" t="s">
         <v>5</v>
@@ -8353,10 +8532,10 @@
         <v>180</v>
       </c>
       <c r="B183" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C183" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D183" s="47" t="s">
         <v>5</v>
@@ -8379,10 +8558,10 @@
         <v>181</v>
       </c>
       <c r="B184" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C184" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D184" s="47" t="s">
         <v>5</v>
@@ -8405,10 +8584,10 @@
         <v>182</v>
       </c>
       <c r="B185" s="43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C185" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D185" s="47" t="s">
         <v>5</v>
@@ -8431,10 +8610,10 @@
         <v>183</v>
       </c>
       <c r="B186" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C186" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D186" s="47" t="s">
         <v>5</v>
@@ -8457,10 +8636,10 @@
         <v>184</v>
       </c>
       <c r="B187" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C187" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D187" s="47" t="s">
         <v>5</v>
@@ -8483,10 +8662,10 @@
         <v>185</v>
       </c>
       <c r="B188" s="43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C188" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D188" s="47" t="s">
         <v>5</v>
@@ -8509,10 +8688,10 @@
         <v>186</v>
       </c>
       <c r="B189" s="43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C189" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D189" s="47" t="s">
         <v>5</v>
@@ -8535,10 +8714,10 @@
         <v>187</v>
       </c>
       <c r="B190" s="43" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C190" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D190" s="47" t="s">
         <v>5</v>
@@ -8561,10 +8740,10 @@
         <v>188</v>
       </c>
       <c r="B191" s="43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C191" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D191" s="47" t="s">
         <v>5</v>
@@ -8587,10 +8766,10 @@
         <v>189</v>
       </c>
       <c r="B192" s="43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C192" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D192" s="47" t="s">
         <v>5</v>
@@ -8613,10 +8792,10 @@
         <v>190</v>
       </c>
       <c r="B193" s="43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C193" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D193" s="47" t="s">
         <v>5</v>
@@ -8639,10 +8818,10 @@
         <v>191</v>
       </c>
       <c r="B194" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C194" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D194" s="47" t="s">
         <v>5</v>
@@ -8665,10 +8844,10 @@
         <v>192</v>
       </c>
       <c r="B195" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C195" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D195" s="47" t="s">
         <v>5</v>
@@ -8691,10 +8870,10 @@
         <v>193</v>
       </c>
       <c r="B196" s="43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C196" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D196" s="47" t="s">
         <v>5</v>
@@ -8717,10 +8896,10 @@
         <v>194</v>
       </c>
       <c r="B197" s="44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C197" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D197" s="47" t="s">
         <v>5</v>
@@ -8743,10 +8922,10 @@
         <v>195</v>
       </c>
       <c r="B198" s="44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C198" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D198" s="47" t="s">
         <v>5</v>
@@ -8769,10 +8948,10 @@
         <v>196</v>
       </c>
       <c r="B199" s="44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C199" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D199" s="47" t="s">
         <v>5</v>
@@ -8795,10 +8974,10 @@
         <v>197</v>
       </c>
       <c r="B200" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C200" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D200" s="47" t="s">
         <v>5</v>
@@ -8821,10 +9000,10 @@
         <v>198</v>
       </c>
       <c r="B201" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C201" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D201" s="47" t="s">
         <v>5</v>
@@ -8847,10 +9026,10 @@
         <v>199</v>
       </c>
       <c r="B202" s="44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C202" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D202" s="47" t="s">
         <v>5</v>
@@ -8873,10 +9052,10 @@
         <v>200</v>
       </c>
       <c r="B203" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C203" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D203" s="47" t="s">
         <v>5</v>
@@ -8899,10 +9078,10 @@
         <v>201</v>
       </c>
       <c r="B204" s="44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C204" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D204" s="47" t="s">
         <v>5</v>
@@ -8925,10 +9104,10 @@
         <v>202</v>
       </c>
       <c r="B205" s="44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C205" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D205" s="47" t="s">
         <v>5</v>
@@ -8951,10 +9130,10 @@
         <v>203</v>
       </c>
       <c r="B206" s="44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C206" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D206" s="47" t="s">
         <v>5</v>
@@ -8977,10 +9156,10 @@
         <v>204</v>
       </c>
       <c r="B207" s="44" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C207" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D207" s="47" t="s">
         <v>5</v>
@@ -9003,10 +9182,10 @@
         <v>205</v>
       </c>
       <c r="B208" s="44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C208" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D208" s="47" t="s">
         <v>5</v>
@@ -9029,10 +9208,10 @@
         <v>206</v>
       </c>
       <c r="B209" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C209" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D209" s="47" t="s">
         <v>5</v>
@@ -9055,10 +9234,10 @@
         <v>207</v>
       </c>
       <c r="B210" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C210" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D210" s="47" t="s">
         <v>5</v>
@@ -9081,10 +9260,10 @@
         <v>208</v>
       </c>
       <c r="B211" s="44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C211" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D211" s="47" t="s">
         <v>5</v>
@@ -9107,10 +9286,10 @@
         <v>209</v>
       </c>
       <c r="B212" s="44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C212" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D212" s="47" t="s">
         <v>5</v>
@@ -9133,10 +9312,10 @@
         <v>210</v>
       </c>
       <c r="B213" s="44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C213" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D213" s="47" t="s">
         <v>5</v>
@@ -9159,10 +9338,10 @@
         <v>211</v>
       </c>
       <c r="B214" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C214" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D214" s="47" t="s">
         <v>5</v>
@@ -9185,10 +9364,10 @@
         <v>212</v>
       </c>
       <c r="B215" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C215" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D215" s="47" t="s">
         <v>5</v>
@@ -9211,10 +9390,10 @@
         <v>213</v>
       </c>
       <c r="B216" s="44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C216" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D216" s="47" t="s">
         <v>5</v>
@@ -9237,10 +9416,10 @@
         <v>214</v>
       </c>
       <c r="B217" s="44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C217" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D217" s="47" t="s">
         <v>5</v>
@@ -9263,10 +9442,10 @@
         <v>215</v>
       </c>
       <c r="B218" s="44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C218" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D218" s="47" t="s">
         <v>5</v>
@@ -9289,10 +9468,10 @@
         <v>216</v>
       </c>
       <c r="B219" s="44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C219" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D219" s="47" t="s">
         <v>5</v>
@@ -9315,10 +9494,10 @@
         <v>217</v>
       </c>
       <c r="B220" s="44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C220" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D220" s="47" t="s">
         <v>5</v>
@@ -9341,10 +9520,10 @@
         <v>218</v>
       </c>
       <c r="B221" s="44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C221" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D221" s="47" t="s">
         <v>5</v>
@@ -9367,10 +9546,10 @@
         <v>219</v>
       </c>
       <c r="B222" s="44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C222" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D222" s="47" t="s">
         <v>5</v>
@@ -9393,10 +9572,10 @@
         <v>220</v>
       </c>
       <c r="B223" s="44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C223" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D223" s="47" t="s">
         <v>5</v>
@@ -9419,10 +9598,10 @@
         <v>221</v>
       </c>
       <c r="B224" s="44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C224" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D224" s="47" t="s">
         <v>5</v>
@@ -9445,10 +9624,10 @@
         <v>222</v>
       </c>
       <c r="B225" s="44" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C225" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D225" s="47" t="s">
         <v>5</v>
@@ -9471,10 +9650,10 @@
         <v>223</v>
       </c>
       <c r="B226" s="44" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C226" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D226" s="47" t="s">
         <v>5</v>
@@ -9497,10 +9676,10 @@
         <v>224</v>
       </c>
       <c r="B227" s="44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C227" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D227" s="47" t="s">
         <v>5</v>
@@ -9523,10 +9702,10 @@
         <v>225</v>
       </c>
       <c r="B228" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C228" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D228" s="47" t="s">
         <v>5</v>
@@ -9549,10 +9728,10 @@
         <v>226</v>
       </c>
       <c r="B229" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C229" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D229" s="47" t="s">
         <v>5</v>
@@ -9575,10 +9754,10 @@
         <v>227</v>
       </c>
       <c r="B230" s="44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C230" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D230" s="47" t="s">
         <v>5</v>
@@ -9601,10 +9780,10 @@
         <v>228</v>
       </c>
       <c r="B231" s="44" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C231" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D231" s="47" t="s">
         <v>5</v>
@@ -9627,10 +9806,10 @@
         <v>229</v>
       </c>
       <c r="B232" s="44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C232" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D232" s="47" t="s">
         <v>5</v>
@@ -9653,10 +9832,10 @@
         <v>230</v>
       </c>
       <c r="B233" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C233" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D233" s="47" t="s">
         <v>5</v>
@@ -9679,10 +9858,10 @@
         <v>231</v>
       </c>
       <c r="B234" s="44" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C234" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D234" s="47" t="s">
         <v>5</v>
@@ -9705,10 +9884,10 @@
         <v>232</v>
       </c>
       <c r="B235" s="44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C235" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D235" s="47" t="s">
         <v>5</v>
@@ -9731,10 +9910,10 @@
         <v>233</v>
       </c>
       <c r="B236" s="44" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C236" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D236" s="47" t="s">
         <v>5</v>
@@ -9757,10 +9936,10 @@
         <v>234</v>
       </c>
       <c r="B237" s="44" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C237" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D237" s="47" t="s">
         <v>5</v>
@@ -9783,10 +9962,10 @@
         <v>235</v>
       </c>
       <c r="B238" s="44" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C238" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D238" s="47" t="s">
         <v>5</v>
@@ -9809,10 +9988,10 @@
         <v>236</v>
       </c>
       <c r="B239" s="44" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C239" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D239" s="47" t="s">
         <v>5</v>
@@ -9835,10 +10014,10 @@
         <v>237</v>
       </c>
       <c r="B240" s="44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C240" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D240" s="47" t="s">
         <v>5</v>
@@ -9861,10 +10040,10 @@
         <v>238</v>
       </c>
       <c r="B241" s="44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C241" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D241" s="47" t="s">
         <v>5</v>
@@ -9887,10 +10066,10 @@
         <v>239</v>
       </c>
       <c r="B242" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C242" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D242" s="47" t="s">
         <v>5</v>
@@ -9913,10 +10092,10 @@
         <v>240</v>
       </c>
       <c r="B243" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C243" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D243" s="47" t="s">
         <v>5</v>
@@ -9939,10 +10118,10 @@
         <v>241</v>
       </c>
       <c r="B244" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C244" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D244" s="47" t="s">
         <v>5</v>
@@ -9965,10 +10144,10 @@
         <v>242</v>
       </c>
       <c r="B245" s="44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C245" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D245" s="47" t="s">
         <v>5</v>
@@ -9991,10 +10170,10 @@
         <v>243</v>
       </c>
       <c r="B246" s="44" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C246" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D246" s="47" t="s">
         <v>5</v>
@@ -10017,10 +10196,10 @@
         <v>244</v>
       </c>
       <c r="B247" s="44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C247" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D247" s="47" t="s">
         <v>5</v>
@@ -10043,10 +10222,10 @@
         <v>245</v>
       </c>
       <c r="B248" s="44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C248" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D248" s="47" t="s">
         <v>5</v>
@@ -10069,10 +10248,10 @@
         <v>246</v>
       </c>
       <c r="B249" s="44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C249" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D249" s="47" t="s">
         <v>5</v>
@@ -10095,10 +10274,10 @@
         <v>247</v>
       </c>
       <c r="B250" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C250" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D250" s="47" t="s">
         <v>5</v>
@@ -10121,10 +10300,10 @@
         <v>248</v>
       </c>
       <c r="B251" s="44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C251" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D251" s="47" t="s">
         <v>5</v>
@@ -10147,10 +10326,10 @@
         <v>249</v>
       </c>
       <c r="B252" s="44" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C252" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D252" s="47" t="s">
         <v>5</v>
@@ -10173,10 +10352,10 @@
         <v>250</v>
       </c>
       <c r="B253" s="44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C253" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D253" s="47" t="s">
         <v>5</v>
@@ -10199,10 +10378,10 @@
         <v>251</v>
       </c>
       <c r="B254" s="44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C254" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D254" s="47" t="s">
         <v>5</v>
@@ -10225,10 +10404,10 @@
         <v>252</v>
       </c>
       <c r="B255" s="44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C255" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D255" s="47" t="s">
         <v>5</v>
@@ -10251,10 +10430,10 @@
         <v>253</v>
       </c>
       <c r="B256" s="44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C256" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D256" s="47" t="s">
         <v>5</v>
@@ -10277,10 +10456,10 @@
         <v>254</v>
       </c>
       <c r="B257" s="44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C257" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D257" s="47" t="s">
         <v>5</v>
@@ -10303,10 +10482,10 @@
         <v>255</v>
       </c>
       <c r="B258" s="44" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C258" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D258" s="47" t="s">
         <v>5</v>
@@ -10329,10 +10508,10 @@
         <v>256</v>
       </c>
       <c r="B259" s="44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C259" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D259" s="47" t="s">
         <v>5</v>
@@ -10355,10 +10534,10 @@
         <v>257</v>
       </c>
       <c r="B260" s="44" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C260" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D260" s="47" t="s">
         <v>5</v>
@@ -10381,10 +10560,10 @@
         <v>258</v>
       </c>
       <c r="B261" s="44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C261" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D261" s="47" t="s">
         <v>5</v>
@@ -10407,10 +10586,10 @@
         <v>259</v>
       </c>
       <c r="B262" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C262" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D262" s="47" t="s">
         <v>5</v>
@@ -10433,10 +10612,10 @@
         <v>260</v>
       </c>
       <c r="B263" s="44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C263" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D263" s="47" t="s">
         <v>5</v>
@@ -10459,10 +10638,10 @@
         <v>261</v>
       </c>
       <c r="B264" s="44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C264" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D264" s="47" t="s">
         <v>5</v>
@@ -10485,10 +10664,10 @@
         <v>262</v>
       </c>
       <c r="B265" s="44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C265" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D265" s="47" t="s">
         <v>5</v>
@@ -10511,10 +10690,10 @@
         <v>263</v>
       </c>
       <c r="B266" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C266" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D266" s="47" t="s">
         <v>5</v>
@@ -10537,10 +10716,10 @@
         <v>264</v>
       </c>
       <c r="B267" s="44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C267" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D267" s="47" t="s">
         <v>5</v>
@@ -10563,10 +10742,10 @@
         <v>265</v>
       </c>
       <c r="B268" s="44" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C268" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D268" s="47" t="s">
         <v>5</v>
@@ -10589,10 +10768,10 @@
         <v>266</v>
       </c>
       <c r="B269" s="44" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C269" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D269" s="47" t="s">
         <v>5</v>
@@ -10615,10 +10794,10 @@
         <v>267</v>
       </c>
       <c r="B270" s="44" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C270" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D270" s="47" t="s">
         <v>5</v>
@@ -10641,10 +10820,10 @@
         <v>268</v>
       </c>
       <c r="B271" s="44" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C271" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D271" s="47" t="s">
         <v>5</v>
@@ -10667,10 +10846,10 @@
         <v>269</v>
       </c>
       <c r="B272" s="44" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C272" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D272" s="47" t="s">
         <v>5</v>
@@ -10693,10 +10872,10 @@
         <v>270</v>
       </c>
       <c r="B273" s="44" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C273" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D273" s="47" t="s">
         <v>5</v>
@@ -10719,10 +10898,10 @@
         <v>271</v>
       </c>
       <c r="B274" s="44" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C274" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D274" s="47" t="s">
         <v>5</v>
@@ -10745,10 +10924,10 @@
         <v>272</v>
       </c>
       <c r="B275" s="44" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C275" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D275" s="47" t="s">
         <v>5</v>
@@ -10771,10 +10950,10 @@
         <v>273</v>
       </c>
       <c r="B276" s="44" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C276" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D276" s="47" t="s">
         <v>5</v>
@@ -10797,10 +10976,10 @@
         <v>274</v>
       </c>
       <c r="B277" s="44" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C277" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D277" s="47" t="s">
         <v>5</v>
@@ -10823,10 +11002,10 @@
         <v>275</v>
       </c>
       <c r="B278" s="44" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C278" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D278" s="47" t="s">
         <v>5</v>
@@ -10849,10 +11028,10 @@
         <v>276</v>
       </c>
       <c r="B279" s="44" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C279" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D279" s="47" t="s">
         <v>5</v>
@@ -10875,10 +11054,10 @@
         <v>277</v>
       </c>
       <c r="B280" s="44" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C280" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D280" s="47" t="s">
         <v>5</v>
@@ -10901,10 +11080,10 @@
         <v>278</v>
       </c>
       <c r="B281" s="44" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C281" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D281" s="47" t="s">
         <v>5</v>
@@ -10927,10 +11106,10 @@
         <v>279</v>
       </c>
       <c r="B282" s="44" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C282" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D282" s="47" t="s">
         <v>5</v>
@@ -10953,10 +11132,10 @@
         <v>280</v>
       </c>
       <c r="B283" s="44" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C283" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D283" s="47" t="s">
         <v>5</v>
@@ -10979,10 +11158,10 @@
         <v>281</v>
       </c>
       <c r="B284" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C284" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D284" s="47" t="s">
         <v>5</v>
@@ -11005,10 +11184,10 @@
         <v>282</v>
       </c>
       <c r="B285" s="44" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C285" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D285" s="47" t="s">
         <v>5</v>
@@ -11031,10 +11210,10 @@
         <v>283</v>
       </c>
       <c r="B286" s="44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C286" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D286" s="47" t="s">
         <v>5</v>
@@ -11057,10 +11236,10 @@
         <v>284</v>
       </c>
       <c r="B287" s="44" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C287" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D287" s="47" t="s">
         <v>5</v>
@@ -11083,10 +11262,10 @@
         <v>285</v>
       </c>
       <c r="B288" s="44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C288" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D288" s="47" t="s">
         <v>5</v>
@@ -11109,10 +11288,10 @@
         <v>286</v>
       </c>
       <c r="B289" s="44" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C289" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D289" s="47" t="s">
         <v>5</v>
@@ -11135,10 +11314,10 @@
         <v>287</v>
       </c>
       <c r="B290" s="44" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C290" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D290" s="47" t="s">
         <v>5</v>
